--- a/applications/pilot_study/positive/seq_pos_pilot.xlsx
+++ b/applications/pilot_study/positive/seq_pos_pilot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Desktop/Doctorado_CEU/HUMAN_QCs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3420736D-B8C3-1A4D-809E-8554A2520A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3020E9A-E058-3F45-A58C-15AC2A29D13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12740" yWindow="6000" windowWidth="25720" windowHeight="15720" xr2:uid="{B0E1915D-E88D-4422-93FC-8C65A0CDB4AB}"/>
+    <workbookView xWindow="3680" yWindow="1780" windowWidth="25720" windowHeight="15720" xr2:uid="{B0E1915D-E88D-4422-93FC-8C65A0CDB4AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <t>sample_name</t>
   </si>
   <si>
-    <t>inj_no</t>
+    <t>injection_index</t>
   </si>
 </sst>
 </file>
@@ -754,7 +754,7 @@
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>105</v>
       </c>
